--- a/AAII_Financials/Quarterly/AGTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGTX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>AGTX</t>
   </si>
@@ -656,114 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43343</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -833,8 +840,14 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -862,14 +875,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
+      <c r="L9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3">
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
@@ -904,8 +917,14 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,14 +952,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
@@ -975,8 +994,14 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,28 +1027,30 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E12" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
       <c r="G12" s="3">
+        <v>200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
@@ -1035,23 +1062,23 @@
         <v>100</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1073,8 +1100,14 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1177,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1194,29 +1233,35 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,13 +1361,15 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
         <v>400</v>
@@ -1328,41 +1381,41 @@
         <v>400</v>
       </c>
       <c r="H17" s="3">
+        <v>400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>400</v>
+      </c>
+      <c r="J17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>200</v>
       </c>
       <c r="M17" s="3">
         <v>200</v>
       </c>
       <c r="N17" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="O17" s="3">
         <v>200</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>200</v>
+      </c>
+      <c r="R17" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
@@ -1379,10 +1432,16 @@
         <v>0</v>
       </c>
       <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1399,41 +1458,41 @@
         <v>-400</v>
       </c>
       <c r="H18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-200</v>
       </c>
       <c r="M18" s="3">
         <v>-200</v>
       </c>
       <c r="N18" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O18" s="3">
         <v>-200</v>
       </c>
       <c r="P18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R18" s="3">
         <v>1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
         <v>0</v>
       </c>
@@ -1450,10 +1509,16 @@
         <v>0</v>
       </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1544,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1488,7 +1555,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1550,8 +1617,14 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1559,7 +1632,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F21" s="3">
         <v>-400</v>
@@ -1568,17 +1641,17 @@
         <v>-400</v>
       </c>
       <c r="H21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1591,18 +1664,18 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
         <v>0</v>
       </c>
@@ -1619,10 +1692,16 @@
         <v>0</v>
       </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1632,11 +1711,11 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
@@ -1647,17 +1726,17 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
@@ -1665,11 +1744,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1692,16 +1771,22 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F23" s="3">
         <v>-400</v>
@@ -1710,41 +1795,41 @@
         <v>-400</v>
       </c>
       <c r="H23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-200</v>
       </c>
       <c r="M23" s="3">
         <v>-200</v>
       </c>
       <c r="N23" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O23" s="3">
         <v>-200</v>
       </c>
       <c r="P23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
@@ -1761,10 +1846,16 @@
         <v>0</v>
       </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1834,8 +1925,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,16 +2002,22 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F26" s="3">
         <v>-400</v>
@@ -1923,41 +2026,41 @@
         <v>-400</v>
       </c>
       <c r="H26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-200</v>
       </c>
       <c r="M26" s="3">
         <v>-200</v>
       </c>
       <c r="N26" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O26" s="3">
         <v>-200</v>
       </c>
       <c r="P26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
@@ -1974,18 +2077,24 @@
         <v>0</v>
       </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F27" s="3">
         <v>-400</v>
@@ -1994,41 +2103,41 @@
         <v>-400</v>
       </c>
       <c r="H27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-200</v>
       </c>
       <c r="M27" s="3">
         <v>-200</v>
       </c>
       <c r="N27" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O27" s="3">
         <v>-200</v>
       </c>
       <c r="P27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
@@ -2045,10 +2154,16 @@
         <v>0</v>
       </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2310,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2464,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2340,7 +2479,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2402,16 +2541,22 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F33" s="3">
         <v>-400</v>
@@ -2420,41 +2565,41 @@
         <v>-400</v>
       </c>
       <c r="H33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-200</v>
       </c>
       <c r="M33" s="3">
         <v>-200</v>
       </c>
       <c r="N33" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O33" s="3">
         <v>-200</v>
       </c>
       <c r="P33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
@@ -2471,10 +2616,16 @@
         <v>0</v>
       </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,16 +2695,22 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F35" s="3">
         <v>-400</v>
@@ -2562,41 +2719,41 @@
         <v>-400</v>
       </c>
       <c r="H35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-200</v>
       </c>
       <c r="M35" s="3">
         <v>-200</v>
       </c>
       <c r="N35" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O35" s="3">
         <v>-200</v>
       </c>
       <c r="P35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
@@ -2613,86 +2770,98 @@
         <v>0</v>
       </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43343</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,8 +2916,10 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2787,14 +2960,14 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
@@ -2816,8 +2989,14 @@
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,8 +3066,14 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2958,25 +3143,31 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
@@ -2991,14 +3182,14 @@
         <v>0</v>
       </c>
       <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3011,11 +3202,11 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3029,55 +3220,61 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
+      <c r="Q45" s="3">
+        <v>100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>100</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
@@ -3088,11 +3285,11 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
@@ -3100,34 +3297,40 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3">
         <v>300</v>
       </c>
       <c r="F46" s="3">
+        <v>300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>300</v>
+      </c>
+      <c r="H46" s="3">
         <v>100</v>
       </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3">
-        <v>0</v>
-      </c>
       <c r="I46" s="3">
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3">
         <v>100</v>
@@ -3142,14 +3345,14 @@
         <v>100</v>
       </c>
       <c r="P46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>100</v>
+      </c>
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -3171,8 +3374,14 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,8 +3451,14 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3313,8 +3528,14 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3605,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3759,14 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3597,8 +3836,14 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,34 +3913,40 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E54" s="3">
         <v>300</v>
       </c>
       <c r="F54" s="3">
+        <v>300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>300</v>
+      </c>
+      <c r="H54" s="3">
         <v>100</v>
       </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3">
-        <v>0</v>
-      </c>
       <c r="I54" s="3">
         <v>0</v>
       </c>
       <c r="J54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3">
         <v>100</v>
@@ -3710,14 +3961,14 @@
         <v>100</v>
       </c>
       <c r="P54" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>100</v>
+      </c>
+      <c r="R54" s="3">
         <v>300</v>
       </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
       <c r="S54" s="3">
         <v>0</v>
       </c>
@@ -3739,8 +3990,14 @@
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,56 +4052,58 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -3864,8 +4125,14 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3875,11 +4142,11 @@
       <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
+      <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
@@ -3890,11 +4157,11 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3920,11 +4187,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>4</v>
@@ -3935,8 +4202,14 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4006,8 +4279,14 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4015,47 +4294,47 @@
         <v>3000</v>
       </c>
       <c r="E60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
@@ -4077,8 +4356,14 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4131,10 +4416,10 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>100</v>
@@ -4143,13 +4428,19 @@
         <v>100</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4219,8 +4510,14 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,8 +4741,14 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4441,55 +4756,55 @@
         <v>3000</v>
       </c>
       <c r="E66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
       <c r="S66" s="3">
         <v>0</v>
       </c>
       <c r="T66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
@@ -4501,10 +4816,16 @@
         <v>100</v>
       </c>
       <c r="Y66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +5078,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,61 +5155,67 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-5400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-4900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-4600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-45300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-44100</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-44000</v>
       </c>
       <c r="U72" s="3">
         <v>-44000</v>
@@ -4877,16 +5224,22 @@
         <v>-44000</v>
       </c>
       <c r="W72" s="3">
-        <v>-43900</v>
+        <v>-44000</v>
       </c>
       <c r="X72" s="3">
-        <v>-43900</v>
+        <v>-44000</v>
       </c>
       <c r="Y72" s="3">
         <v>-43900</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>-43900</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,64 +5463,70 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-2700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-200</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3">
         <v>200</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
       <c r="T76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V76" s="3">
         <v>-100</v>
@@ -5167,10 +5538,16 @@
         <v>-100</v>
       </c>
       <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,92 +5617,104 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43343</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="F81" s="3">
         <v>-400</v>
@@ -5334,41 +5723,41 @@
         <v>-400</v>
       </c>
       <c r="H81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-200</v>
       </c>
       <c r="M81" s="3">
         <v>-200</v>
       </c>
       <c r="N81" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="O81" s="3">
         <v>-200</v>
       </c>
       <c r="P81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
@@ -5385,10 +5774,16 @@
         <v>0</v>
       </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5809,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5485,8 +5882,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,20 +6267,26 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
         <v>0</v>
       </c>
@@ -5873,23 +6306,23 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
@@ -5911,8 +6344,14 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6377,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6009,8 +6450,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6604,14 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6195,11 +6654,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
@@ -6210,11 +6669,11 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6222,8 +6681,14 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6714,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6787,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,8 +7018,14 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6542,10 +7033,10 @@
         <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
       </c>
       <c r="G100" s="3">
         <v>100</v>
@@ -6554,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -6566,23 +7057,23 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -6604,8 +7095,14 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6615,11 +7112,11 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
@@ -6630,11 +7127,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6675,8 +7172,14 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6714,17 +7217,17 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -6744,6 +7247,12 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AGTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>AGTX</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43343</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -846,8 +850,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -881,11 +888,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -923,8 +930,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -958,11 +968,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,19 +1042,20 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>-100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
@@ -1050,38 +1064,38 @@
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
       <c r="N12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1239,29 +1259,32 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,8 +1389,9 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1372,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
         <v>400</v>
@@ -1387,16 +1414,16 @@
         <v>400</v>
       </c>
       <c r="J17" s="3">
+        <v>400</v>
+      </c>
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>200</v>
       </c>
       <c r="N17" s="3">
         <v>200</v>
@@ -1405,20 +1432,20 @@
         <v>200</v>
       </c>
       <c r="P17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
@@ -1438,10 +1465,13 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1449,7 +1479,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>-400</v>
@@ -1464,16 +1494,16 @@
         <v>-400</v>
       </c>
       <c r="J18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-200</v>
       </c>
       <c r="N18" s="3">
         <v>-200</v>
@@ -1482,20 +1512,20 @@
         <v>-200</v>
       </c>
       <c r="P18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
@@ -1515,10 +1545,13 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1555,11 +1589,11 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1623,8 +1657,11 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1632,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-400</v>
       </c>
       <c r="G21" s="3">
         <v>-400</v>
@@ -1647,14 +1684,14 @@
         <v>-400</v>
       </c>
       <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1670,15 +1707,15 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
       <c r="U21" s="3">
         <v>0</v>
       </c>
@@ -1698,10 +1735,13 @@
         <v>0</v>
       </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1717,8 +1757,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>4</v>
@@ -1732,14 +1772,14 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
@@ -1750,8 +1790,8 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1777,8 +1817,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1786,10 +1829,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-400</v>
       </c>
       <c r="G23" s="3">
         <v>-400</v>
@@ -1801,16 +1844,16 @@
         <v>-400</v>
       </c>
       <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-200</v>
       </c>
       <c r="N23" s="3">
         <v>-200</v>
@@ -1819,20 +1862,20 @@
         <v>-200</v>
       </c>
       <c r="P23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
@@ -1852,10 +1895,13 @@
         <v>0</v>
       </c>
       <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,8 +2057,11 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2017,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-400</v>
       </c>
       <c r="G26" s="3">
         <v>-400</v>
@@ -2032,16 +2084,16 @@
         <v>-400</v>
       </c>
       <c r="J26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-200</v>
       </c>
       <c r="N26" s="3">
         <v>-200</v>
@@ -2050,20 +2102,20 @@
         <v>-200</v>
       </c>
       <c r="P26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
@@ -2083,10 +2135,13 @@
         <v>0</v>
       </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2094,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-400</v>
       </c>
       <c r="G27" s="3">
         <v>-400</v>
@@ -2109,16 +2164,16 @@
         <v>-400</v>
       </c>
       <c r="J27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-200</v>
       </c>
       <c r="N27" s="3">
         <v>-200</v>
@@ -2127,20 +2182,20 @@
         <v>-200</v>
       </c>
       <c r="P27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
@@ -2160,10 +2215,13 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2479,11 +2549,11 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2547,8 +2617,11 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2556,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-400</v>
       </c>
       <c r="G33" s="3">
         <v>-400</v>
@@ -2571,16 +2644,16 @@
         <v>-400</v>
       </c>
       <c r="J33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-200</v>
       </c>
       <c r="N33" s="3">
         <v>-200</v>
@@ -2589,20 +2662,20 @@
         <v>-200</v>
       </c>
       <c r="P33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
@@ -2622,10 +2695,13 @@
         <v>0</v>
       </c>
       <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,8 +2777,11 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2710,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-400</v>
       </c>
       <c r="G35" s="3">
         <v>-400</v>
@@ -2725,16 +2804,16 @@
         <v>-400</v>
       </c>
       <c r="J35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-200</v>
       </c>
       <c r="N35" s="3">
         <v>-200</v>
@@ -2743,20 +2822,20 @@
         <v>-200</v>
       </c>
       <c r="P35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
@@ -2776,92 +2855,98 @@
         <v>0</v>
       </c>
       <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43343</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,8 +3004,9 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2966,11 +3053,11 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -2995,8 +3082,11 @@
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,8 +3162,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3188,11 +3284,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3208,8 +3304,8 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3226,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3235,20 +3334,20 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
         <v>0</v>
       </c>
@@ -3258,17 +3357,17 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3276,8 +3375,8 @@
       <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
+      <c r="S45" s="3">
+        <v>100</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
@@ -3291,8 +3390,8 @@
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="X45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3303,8 +3402,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3312,7 +3414,7 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F46" s="3">
         <v>300</v>
@@ -3321,11 +3423,11 @@
         <v>300</v>
       </c>
       <c r="H46" s="3">
+        <v>300</v>
+      </c>
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
       <c r="J46" s="3">
         <v>0</v>
       </c>
@@ -3333,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M46" s="3">
         <v>100</v>
@@ -3351,11 +3453,11 @@
         <v>100</v>
       </c>
       <c r="R46" s="3">
+        <v>100</v>
+      </c>
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,8 +3562,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3534,8 +3642,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,8 +4042,11 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3928,7 +4054,7 @@
         <v>100</v>
       </c>
       <c r="E54" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F54" s="3">
         <v>300</v>
@@ -3937,11 +4063,11 @@
         <v>300</v>
       </c>
       <c r="H54" s="3">
+        <v>300</v>
+      </c>
+      <c r="I54" s="3">
         <v>100</v>
       </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
       <c r="J54" s="3">
         <v>0</v>
       </c>
@@ -3949,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" s="3">
         <v>100</v>
@@ -3967,11 +4093,11 @@
         <v>100</v>
       </c>
       <c r="R54" s="3">
+        <v>100</v>
+      </c>
+      <c r="S54" s="3">
         <v>300</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
       <c r="T54" s="3">
         <v>0</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,58 +4184,59 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -4131,8 +4262,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4148,8 +4282,8 @@
       <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
+      <c r="H58" s="3">
+        <v>100</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
@@ -4163,8 +4297,8 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4193,8 +4327,8 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
@@ -4208,8 +4342,11 @@
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4285,58 +4422,61 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>100</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
       </c>
       <c r="S60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>0</v>
@@ -4362,8 +4502,11 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4422,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>100</v>
@@ -4434,13 +4577,16 @@
         <v>100</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,58 +4902,61 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>300</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>100</v>
       </c>
       <c r="R66" s="3">
         <v>100</v>
       </c>
       <c r="S66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T66" s="3">
         <v>0</v>
@@ -4807,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W66" s="3">
         <v>100</v>
@@ -4822,10 +4980,13 @@
         <v>100</v>
       </c>
       <c r="AA66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,8 +5332,11 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5173,52 +5347,52 @@
         <v>-6000</v>
       </c>
       <c r="F72" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G72" s="3">
         <v>-5800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-45300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-44100</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-44000</v>
       </c>
       <c r="V72" s="3">
         <v>-44000</v>
@@ -5230,7 +5404,7 @@
         <v>-44000</v>
       </c>
       <c r="Y72" s="3">
-        <v>-43900</v>
+        <v>-44000</v>
       </c>
       <c r="Z72" s="3">
         <v>-43900</v>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3">
         <v>-43900</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>-43900</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,59 +5652,62 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-2800</v>
+        <v>-2600</v>
       </c>
       <c r="E76" s="3">
         <v>-2800</v>
       </c>
       <c r="F76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G76" s="3">
         <v>-2700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-200</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
+        <v>0</v>
+      </c>
+      <c r="S76" s="3">
         <v>200</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
@@ -5529,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W76" s="3">
         <v>-100</v>
@@ -5544,10 +5730,13 @@
         <v>-100</v>
       </c>
       <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,90 +5812,96 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43343</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43251</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5714,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-400</v>
       </c>
       <c r="G81" s="3">
         <v>-400</v>
@@ -5729,16 +5924,16 @@
         <v>-400</v>
       </c>
       <c r="J81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-200</v>
       </c>
       <c r="N81" s="3">
         <v>-200</v>
@@ -5747,20 +5942,20 @@
         <v>-200</v>
       </c>
       <c r="P81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
@@ -5780,10 +5975,13 @@
         <v>0</v>
       </c>
       <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-42700</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6009,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,23 +6487,26 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
@@ -6312,20 +6529,20 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6837,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6660,8 +6890,8 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
@@ -6675,8 +6905,8 @@
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,32 +7267,35 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>100</v>
       </c>
       <c r="G100" s="3">
         <v>100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -7063,20 +7309,20 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7118,8 +7367,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
@@ -7133,8 +7382,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7178,8 +7427,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7223,14 +7475,14 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>
